--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:40+00:00</t>
+    <t>2026-04-20T06:44:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5513,7 +5513,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>176</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T06:44:24+00:00</t>
+    <t>2026-04-20T07:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-liste-des-allergies-et-hypersensibilites.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:29:37+00:00</t>
+    <t>2026-04-20T13:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
